--- a/excel/signalements.xlsx
+++ b/excel/signalements.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nevatunca/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hessoit-my.sharepoint.com/personal/neva_tunca_hes-so_ch/Documents/COM semestre 2/InfraDon/Renouvellement-du-parc-de-bancs/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{439CCFEC-3998-2C49-928B-831BD6FDF48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{439CCFEC-3998-2C49-928B-831BD6FDF48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A77B57-9D36-FE4F-A71D-18396C2FE0D7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1510,6 +1510,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="25.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
